--- a/public/story-map-template.xlsx
+++ b/public/story-map-template.xlsx
@@ -31,7 +31,7 @@
     <t>Why, in one line</t>
   </si>
   <si>
-    <t>Start a story with ? when it is assumed, not yet checked with your partner: the cell turns amber, and the question goes on the Questions for our partner tab. A story without ? is known.</t>
+    <t>Start a story with ? when it is assumed, not yet checked with your partner: the cell turns amber, and the question goes on the Questions for our partner tab. A story without ? is known. To submit, export the whole workbook, both tabs, as one PDF (in Google Sheets, choose Workbook, not Current sheet).</t>
   </si>
   <si>
     <r>
@@ -714,7 +714,7 @@
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
     </row>
-    <row r="4" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>4</v>
       </c>

--- a/public/story-map-template.xlsx
+++ b/public/story-map-template.xlsx
@@ -31,7 +31,7 @@
     <t>Why, in one line</t>
   </si>
   <si>
-    <t>Start a story with ? when it is assumed, not yet checked with your partner: the cell turns amber, and the question goes on the Questions for our partner tab. A story without ? is known. To submit, export the whole workbook, both tabs, as one PDF (in Google Sheets, choose Workbook, not Current sheet).</t>
+    <t>Start a story with ? when it is assumed, not yet checked with your partner: the cell turns amber, and the question goes on the Questions for our partner tab. A story without ? is known. Insert a row for each release after Release 1 (Release 2, Release 3), above Out of scope this year. More than one kind of user? Draw one map: follow the primary user's flow, and add parallel columns only where another user's path diverges. To submit, export the whole workbook, both tabs, as one PDF (in Google Sheets, choose Workbook, not Current sheet).</t>
   </si>
   <si>
     <r>
@@ -72,7 +72,7 @@
         <rFont val="Arial"/>
       </rPr>
       <t xml:space="preserve">
-One story under every column, however thin.</t>
+One story under every column, however thin. Built in the fall.</t>
     </r>
   </si>
   <si>
@@ -93,7 +93,7 @@
         <rFont val="Arial"/>
       </rPr>
       <t xml:space="preserve">
-The next slice.</t>
+The first iteration after the walking skeleton. Insert more release rows below it as needed.</t>
     </r>
   </si>
   <si>
@@ -714,7 +714,7 @@
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
     </row>
-    <row r="4" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" ht="60" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>4</v>
       </c>

--- a/public/story-map-template.xlsx
+++ b/public/story-map-template.xlsx
@@ -93,7 +93,7 @@
         <rFont val="Arial"/>
       </rPr>
       <t xml:space="preserve">
-The first iteration after the walking skeleton. Insert more release rows below it as needed.</t>
+The first iteration after the walking skeleton.</t>
     </r>
   </si>
   <si>

--- a/public/story-map-template.xlsx
+++ b/public/story-map-template.xlsx
@@ -31,7 +31,7 @@
     <t>Why, in one line</t>
   </si>
   <si>
-    <t>Start a story with ? when it is assumed, not yet checked with your partner: the cell turns amber, and the question goes on the Questions for our partner tab. A story without ? is known. To submit, export the whole workbook, both tabs, as one PDF (in Google Sheets, choose Workbook, not Current sheet).</t>
+    <t>Start a story with ? when it is assumed, not yet checked with your partner: the cell turns amber, and the question goes on the Questions for our partner tab. A story without ? is known. Insert a row for each release after Release 1 (Release 2, Release 3), above Out of scope this year. More than one kind of user? Draw one map: follow the primary user's flow, and add parallel columns only where another user's path diverges. To submit, export the whole workbook, both tabs, as one PDF (in Google Sheets, choose Workbook, not Current sheet).</t>
   </si>
   <si>
     <r>
@@ -72,7 +72,7 @@
         <rFont val="Arial"/>
       </rPr>
       <t xml:space="preserve">
-One story under every column, however thin.</t>
+One story under every column, however thin. Built in the fall.</t>
     </r>
   </si>
   <si>
@@ -93,7 +93,7 @@
         <rFont val="Arial"/>
       </rPr>
       <t xml:space="preserve">
-The next slice.</t>
+The first iteration after the walking skeleton.</t>
     </r>
   </si>
   <si>
@@ -714,7 +714,7 @@
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
     </row>
-    <row r="4" ht="44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" ht="60" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>4</v>
       </c>
